--- a/server/data/Student_Mock_Data.xlsx
+++ b/server/data/Student_Mock_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\OneDrive\画像\Desktop\Next Gen\PBL_Project\server\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\munab\OneDrive\Documents\Custom Office Templates\OneDrive\Desktop\PBL\PBL_Project\server\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A001114D-811D-4EAE-9EBC-38B7C406D5E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068306A2-9CE3-41B4-8DD9-C84376AC4569}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="8880" xr2:uid="{1DA6C248-F2D4-4D82-AF95-8A3F84EF0074}"/>
   </bookViews>
@@ -20,21 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>roll_number</t>
   </si>
@@ -57,74 +48,55 @@
     <t>twelfth_marks</t>
   </si>
   <si>
-    <t>CSE26001</t>
-  </si>
-  <si>
-    <t>aditi.sharma@college.edu</t>
-  </si>
-  <si>
-    <t>CSE26002</t>
-  </si>
-  <si>
-    <t>rahul.verma@college.edu</t>
-  </si>
-  <si>
-    <t>CSE26003</t>
-  </si>
-  <si>
-    <t>priya.patel@college.edu</t>
-  </si>
-  <si>
-    <t>IT26001</t>
-  </si>
-  <si>
-    <t>rohan.singh@college.edu</t>
-  </si>
-  <si>
-    <t>IT26002</t>
-  </si>
-  <si>
-    <t>neha.gupta@college.edu</t>
-  </si>
-  <si>
-    <t>ECE26001</t>
-  </si>
-  <si>
-    <t>karan.malhotra@college.edu</t>
-  </si>
-  <si>
-    <t>ECE26002</t>
-  </si>
-  <si>
-    <t>sneha.joshi@college.edu</t>
-  </si>
-  <si>
-    <t>EEE26001</t>
-  </si>
-  <si>
-    <t>vikram.rathore@college.edu</t>
-  </si>
-  <si>
-    <t>ME26001</t>
-  </si>
-  <si>
-    <t>arjun.nair@college.edu</t>
-  </si>
-  <si>
-    <t>CE26001</t>
-  </si>
-  <si>
-    <t>pooja.desai@college.edu</t>
+    <t>CE0079</t>
+  </si>
+  <si>
+    <t>tempaman97@gmail.com</t>
+  </si>
+  <si>
+    <t>CE</t>
+  </si>
+  <si>
+    <t>IT0045</t>
+  </si>
+  <si>
+    <t>shritejnehere@gmail.com</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>ENTC0089</t>
+  </si>
+  <si>
+    <t>pranavoswal21@gmaiil.com</t>
+  </si>
+  <si>
+    <t>ENTC</t>
+  </si>
+  <si>
+    <t>ENTC 0081</t>
+  </si>
+  <si>
+    <t>atharvacoolkarni24@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -147,13 +119,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -466,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF9E9C4D-32AB-46E6-8EA9-BF9A8998E320}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -504,233 +479,101 @@
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2">
-        <v>1</v>
+      <c r="C2" t="s">
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>8.8000000000000007</v>
+        <v>9.9</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>92.5</v>
+        <v>99</v>
       </c>
       <c r="G2">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3">
-        <v>1</v>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
       </c>
       <c r="D3">
-        <v>7.4</v>
+        <v>9.99</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G3">
-        <v>76.5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
       </c>
       <c r="D4">
-        <v>9.1999999999999993</v>
+        <v>9.89</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G4">
-        <v>91.2</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>8.1</v>
+        <v>9.11</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G5">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>6.9</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>78.5</v>
-      </c>
-      <c r="G6">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>7.8</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>88</v>
-      </c>
-      <c r="G7">
-        <v>84.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>8.5</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>90.5</v>
-      </c>
-      <c r="G8">
-        <v>87.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9">
-        <v>7.1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>76</v>
-      </c>
-      <c r="G9">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10">
-        <v>5</v>
-      </c>
-      <c r="D10">
-        <v>8</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>82.5</v>
-      </c>
-      <c r="G10">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11">
-        <v>6</v>
-      </c>
-      <c r="D11">
-        <v>8.4</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>86</v>
-      </c>
-      <c r="G11">
-        <v>83.5</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{860CB7EC-0BEE-4A58-AE0D-EBF0C21063B9}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{C216BB71-AE7C-43EC-960E-C05A9BC19E76}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{B461DC2A-F2AC-4C81-BAF1-BC86121AE1E0}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{73FC1AA2-023C-4B69-A06B-B364150C599F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>